--- a/o-assets/mẫu import học sinh.xlsx
+++ b/o-assets/mẫu import học sinh.xlsx
@@ -1,88 +1,97 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10308"/>
-  <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/xuanhoa/Desktop/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D88F4E24-A9BA-F747-ABCD-A6AD5CB2CC3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
+  <fileVersion appName="Calc" lowestEdited="7"/>
+  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="3260" yWindow="2260" windowWidth="28040" windowHeight="17180" xr2:uid="{4A2374B1-833E-2841-A44A-319304B1B95D}"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
+    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
+      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
-  <si>
-    <t>STT</t>
-  </si>
-  <si>
-    <t>Khối</t>
-  </si>
-  <si>
-    <t>Lớp</t>
-  </si>
-  <si>
-    <t>Mã học sinh</t>
-  </si>
-  <si>
-    <t>Tên học sinh</t>
-  </si>
-  <si>
-    <t>Số điện thoại</t>
-  </si>
-  <si>
-    <t>Email(không bắt buộc)</t>
-  </si>
-  <si>
-    <t>Mật khẩu</t>
-  </si>
-  <si>
-    <t>Ngày sinh (Không bắt buộc)</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+  <si>
+    <t xml:space="preserve">Tên trường:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Địa chỉ trường:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Khối</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lớp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mã học sinh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tên học sinh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Số điện thoại</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mật khẩu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Email(không bắt buộc)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ngày sinh (Không bắt buộc)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="General"/>
+  </numFmts>
+  <fonts count="5">
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
-      <scheme val="minor"/>
+      <charset val="1"/>
     </font>
     <font>
-      <b/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <b val="true"/>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
-      <scheme val="minor"/>
+      <family val="0"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -94,70 +103,146 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-4.9989318521683403E-2"/>
-        <bgColor indexed="64"/>
+        <fgColor theme="0" tint="-0.05"/>
+        <bgColor rgb="FFFFFFCC"/>
       </patternFill>
     </fill>
   </fills>
   <borders count="2">
-    <border>
+    <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  <cellStyleXfs count="20">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
   <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="15" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
+    <cellStyle name="Currency" xfId="17" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
+    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="FF000000"/>
+      <rgbColor rgb="FFF2F2F2"/>
+      <rgbColor rgb="FFFF0000"/>
+      <rgbColor rgb="FF00FF00"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF008000"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FF808000"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FFC0C0C0"/>
+      <rgbColor rgb="FF808080"/>
+      <rgbColor rgb="FF9999FF"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FFFFFFCC"/>
+      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FF660066"/>
+      <rgbColor rgb="FFFF8080"/>
+      <rgbColor rgb="FF0066CC"/>
+      <rgbColor rgb="FFCCCCFF"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FF00CCFF"/>
+      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFCCFFCC"/>
+      <rgbColor rgb="FFFFFF99"/>
+      <rgbColor rgb="FF99CCFF"/>
+      <rgbColor rgb="FFFF99CC"/>
+      <rgbColor rgb="FFCC99FF"/>
+      <rgbColor rgb="FFFFCC99"/>
+      <rgbColor rgb="FF3366FF"/>
+      <rgbColor rgb="FF33CCCC"/>
+      <rgbColor rgb="FF99CC00"/>
+      <rgbColor rgb="FFFFCC00"/>
+      <rgbColor rgb="FFFF9900"/>
+      <rgbColor rgb="FFFF6600"/>
+      <rgbColor rgb="FF666699"/>
+      <rgbColor rgb="FF969696"/>
+      <rgbColor rgb="FF003366"/>
+      <rgbColor rgb="FF339966"/>
+      <rgbColor rgb="FF003300"/>
+      <rgbColor rgb="FF333300"/>
+      <rgbColor rgb="FF993300"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FF333399"/>
+      <rgbColor rgb="FF333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
+        <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="0E2841"/>
@@ -192,153 +277,55 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:latin typeface="Aptos Display" panose="02110004020202020204" pitchFamily="0" charset="1"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:latin typeface="Aptos Narrow" panose="02110004020202020204" pitchFamily="0" charset="1"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme>
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
                 <a:tint val="67000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
                 <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
                 <a:tint val="73000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
                 <a:tint val="81000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
                 <a:lumMod val="102000"/>
                 <a:tint val="94000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
                 <a:lumMod val="100000"/>
                 <a:shade val="100000"/>
               </a:schemeClr>
@@ -346,33 +333,24 @@
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
                 <a:shade val="78000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
         <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
@@ -385,13 +363,7 @@
           <a:effectLst/>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
+          <a:effectLst/>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
@@ -401,15 +373,13 @@
         <a:solidFill>
           <a:schemeClr val="phClr">
             <a:tint val="95000"/>
-            <a:satMod val="170000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="93000"/>
-                <a:satMod val="150000"/>
                 <a:shade val="98000"/>
                 <a:lumMod val="102000"/>
               </a:schemeClr>
@@ -417,7 +387,6 @@
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
                 <a:tint val="98000"/>
-                <a:satMod val="130000"/>
                 <a:shade val="90000"/>
                 <a:lumMod val="103000"/>
               </a:schemeClr>
@@ -425,119 +394,71 @@
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="63000"/>
-                <a:satMod val="120000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{549CF3D7-A080-CF43-A852-301C061852E7}">
-  <dimension ref="A1:I33"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:I36"/>
+  <sheetFormatPr defaultColWidth="10.55078125" defaultRowHeight="15.75" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="6" max="6" width="11.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.5" customWidth="1"/>
-    <col min="8" max="8" width="19.1640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="23.83203125" bestFit="1" customWidth="1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="0" width="11.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="19.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="23.83"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="0" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+    </row>
+    <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="0" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+    </row>
+    <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="B4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="C4" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="D4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="E4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" s="1" t="s">
+      <c r="G4" s="1" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A2" s="2"/>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A3" s="2"/>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2"/>
-      <c r="I3" s="2"/>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A4" s="2"/>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
-      <c r="I4" s="2"/>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="H4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -548,7 +469,7 @@
       <c r="H5" s="2"/>
       <c r="I5" s="2"/>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
@@ -559,7 +480,7 @@
       <c r="H6" s="2"/>
       <c r="I6" s="2"/>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2"/>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
@@ -570,7 +491,7 @@
       <c r="H7" s="2"/>
       <c r="I7" s="2"/>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
@@ -581,7 +502,7 @@
       <c r="H8" s="2"/>
       <c r="I8" s="2"/>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
@@ -592,7 +513,7 @@
       <c r="H9" s="2"/>
       <c r="I9" s="2"/>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
@@ -603,7 +524,7 @@
       <c r="H10" s="2"/>
       <c r="I10" s="2"/>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
@@ -614,7 +535,7 @@
       <c r="H11" s="2"/>
       <c r="I11" s="2"/>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
@@ -625,7 +546,7 @@
       <c r="H12" s="2"/>
       <c r="I12" s="2"/>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
@@ -636,7 +557,7 @@
       <c r="H13" s="2"/>
       <c r="I13" s="2"/>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
@@ -647,7 +568,7 @@
       <c r="H14" s="2"/>
       <c r="I14" s="2"/>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2"/>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
@@ -658,7 +579,7 @@
       <c r="H15" s="2"/>
       <c r="I15" s="2"/>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2"/>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
@@ -669,7 +590,7 @@
       <c r="H16" s="2"/>
       <c r="I16" s="2"/>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2"/>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
@@ -680,7 +601,7 @@
       <c r="H17" s="2"/>
       <c r="I17" s="2"/>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="2"/>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
@@ -691,7 +612,7 @@
       <c r="H18" s="2"/>
       <c r="I18" s="2"/>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="2"/>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
@@ -702,7 +623,7 @@
       <c r="H19" s="2"/>
       <c r="I19" s="2"/>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="20" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="2"/>
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
@@ -713,7 +634,7 @@
       <c r="H20" s="2"/>
       <c r="I20" s="2"/>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="2"/>
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
@@ -724,7 +645,7 @@
       <c r="H21" s="2"/>
       <c r="I21" s="2"/>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
@@ -735,7 +656,7 @@
       <c r="H22" s="2"/>
       <c r="I22" s="2"/>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="2"/>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
@@ -746,7 +667,7 @@
       <c r="H23" s="2"/>
       <c r="I23" s="2"/>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="24" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
@@ -757,7 +678,7 @@
       <c r="H24" s="2"/>
       <c r="I24" s="2"/>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="25" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="2"/>
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
@@ -768,7 +689,7 @@
       <c r="H25" s="2"/>
       <c r="I25" s="2"/>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="26" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
@@ -779,7 +700,7 @@
       <c r="H26" s="2"/>
       <c r="I26" s="2"/>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="27" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="2"/>
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
@@ -790,7 +711,7 @@
       <c r="H27" s="2"/>
       <c r="I27" s="2"/>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="28" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="2"/>
       <c r="B28" s="2"/>
       <c r="C28" s="2"/>
@@ -801,7 +722,7 @@
       <c r="H28" s="2"/>
       <c r="I28" s="2"/>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="29" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="2"/>
       <c r="B29" s="2"/>
       <c r="C29" s="2"/>
@@ -812,7 +733,7 @@
       <c r="H29" s="2"/>
       <c r="I29" s="2"/>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="30" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="2"/>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
@@ -823,7 +744,7 @@
       <c r="H30" s="2"/>
       <c r="I30" s="2"/>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="31" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="2"/>
       <c r="B31" s="2"/>
       <c r="C31" s="2"/>
@@ -834,7 +755,7 @@
       <c r="H31" s="2"/>
       <c r="I31" s="2"/>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="32" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="2"/>
       <c r="B32" s="2"/>
       <c r="C32" s="2"/>
@@ -845,7 +766,7 @@
       <c r="H32" s="2"/>
       <c r="I32" s="2"/>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="33" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="2"/>
       <c r="B33" s="2"/>
       <c r="C33" s="2"/>
@@ -856,8 +777,46 @@
       <c r="H33" s="2"/>
       <c r="I33" s="2"/>
     </row>
+    <row r="34" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="2"/>
+      <c r="B34" s="2"/>
+      <c r="C34" s="2"/>
+      <c r="D34" s="2"/>
+      <c r="E34" s="2"/>
+      <c r="F34" s="2"/>
+      <c r="G34" s="2"/>
+      <c r="H34" s="2"/>
+      <c r="I34" s="2"/>
+    </row>
+    <row r="35" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="2"/>
+      <c r="B35" s="2"/>
+      <c r="C35" s="2"/>
+      <c r="D35" s="2"/>
+      <c r="E35" s="2"/>
+      <c r="F35" s="2"/>
+      <c r="G35" s="2"/>
+      <c r="H35" s="2"/>
+      <c r="I35" s="2"/>
+    </row>
+    <row r="36" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="2"/>
+      <c r="B36" s="2"/>
+      <c r="C36" s="2"/>
+      <c r="D36" s="2"/>
+      <c r="E36" s="2"/>
+      <c r="F36" s="2"/>
+      <c r="G36" s="2"/>
+      <c r="H36" s="2"/>
+      <c r="I36" s="2"/>
+    </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
 </worksheet>
 </file>